--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488280_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488280_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.1792</v>
+        <v>4.8334</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.0591</v>
+        <v>-0.2981</v>
       </c>
       <c r="F2" t="n">
-        <v>5.2382</v>
+        <v>5.1315</v>
       </c>
       <c r="G2" t="n">
         <v>1.9865</v>
@@ -610,13 +610,13 @@
         <v>1.4823</v>
       </c>
       <c r="S2" t="n">
-        <v>2.0068</v>
+        <v>1.661</v>
       </c>
       <c r="T2" t="n">
-        <v>0.2661</v>
+        <v>0.0271</v>
       </c>
       <c r="U2" t="n">
-        <v>1.7407</v>
+        <v>1.634</v>
       </c>
       <c r="V2" t="n">
         <v>0.63</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.2916</v>
+        <v>4.0329</v>
       </c>
       <c r="E3" t="n">
-        <v>0.3941</v>
+        <v>0.9385</v>
       </c>
       <c r="F3" t="n">
-        <v>2.8975</v>
+        <v>3.0944</v>
       </c>
       <c r="G3" t="n">
         <v>5.8023</v>
@@ -688,13 +688,13 @@
         <v>0.7411</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0132</v>
+        <v>0.7544999999999999</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.9849</v>
+        <v>-0.4405</v>
       </c>
       <c r="U3" t="n">
-        <v>0.998</v>
+        <v>1.195</v>
       </c>
       <c r="V3" t="n">
         <v>0.4407</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.7371</v>
+        <v>0.6391</v>
       </c>
       <c r="E4" t="n">
-        <v>0.2714</v>
+        <v>-0.4574</v>
       </c>
       <c r="F4" t="n">
-        <v>1.4658</v>
+        <v>1.0964</v>
       </c>
       <c r="G4" t="n">
         <v>0.7895</v>
@@ -766,13 +766,13 @@
         <v>0.9264</v>
       </c>
       <c r="S4" t="n">
-        <v>2.7097</v>
+        <v>1.6116</v>
       </c>
       <c r="T4" t="n">
-        <v>1.2473</v>
+        <v>0.5185999999999999</v>
       </c>
       <c r="U4" t="n">
-        <v>1.4624</v>
+        <v>1.093</v>
       </c>
       <c r="V4" t="n">
         <v>-1.7621</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>R. VINCENT MAGO</t>
+          <t>J. BARRIENTOS PRIETO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.7032</v>
+        <v>0.4225</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.8873</v>
+        <v>-3.3573</v>
       </c>
       <c r="F5" t="n">
-        <v>1.5906</v>
+        <v>3.7798</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.8487</v>
+        <v>2.2964</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.8873</v>
+        <v>1.8308</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0386</v>
+        <v>0.4656</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.3912</v>
+        <v>1.4018</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.3912</v>
+        <v>1.8888</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>-0.487</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.4575</v>
+        <v>0.8946</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.4961</v>
+        <v>-0.058</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0386</v>
+        <v>0.9526</v>
       </c>
       <c r="P5" t="n">
-        <v>0.3706</v>
+        <v>-3.1499</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.9264</v>
+        <v>-4.6322</v>
       </c>
       <c r="R5" t="n">
-        <v>1.297</v>
+        <v>1.4823</v>
       </c>
       <c r="S5" t="n">
-        <v>1.1814</v>
+        <v>1.1503</v>
       </c>
       <c r="T5" t="n">
-        <v>0.4303</v>
+        <v>-0.4414</v>
       </c>
       <c r="U5" t="n">
-        <v>0.7511</v>
+        <v>1.5917</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>0.1257</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>0.3144</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-0.1888</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. BARRIENTOS PRIETO</t>
+          <t>R. VINCENT MAGO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.5894</v>
+        <v>0.0429</v>
       </c>
       <c r="E6" t="n">
-        <v>-3.4121</v>
+        <v>-1.6708</v>
       </c>
       <c r="F6" t="n">
-        <v>4.0014</v>
+        <v>1.7137</v>
       </c>
       <c r="G6" t="n">
-        <v>2.2964</v>
+        <v>-0.8487</v>
       </c>
       <c r="H6" t="n">
-        <v>1.8308</v>
+        <v>-0.8873</v>
       </c>
       <c r="I6" t="n">
-        <v>0.4656</v>
+        <v>0.0386</v>
       </c>
       <c r="J6" t="n">
-        <v>1.4018</v>
+        <v>-0.3912</v>
       </c>
       <c r="K6" t="n">
-        <v>1.8888</v>
+        <v>-0.3912</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.487</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>0.8946</v>
+        <v>-0.4575</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.058</v>
+        <v>-0.4961</v>
       </c>
       <c r="O6" t="n">
-        <v>0.9526</v>
+        <v>0.0386</v>
       </c>
       <c r="P6" t="n">
-        <v>-3.1499</v>
+        <v>0.3706</v>
       </c>
       <c r="Q6" t="n">
-        <v>-4.6322</v>
+        <v>-0.9264</v>
       </c>
       <c r="R6" t="n">
-        <v>1.4823</v>
+        <v>1.297</v>
       </c>
       <c r="S6" t="n">
-        <v>1.3171</v>
+        <v>0.521</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.4961</v>
+        <v>-0.3531</v>
       </c>
       <c r="U6" t="n">
-        <v>1.8133</v>
+        <v>0.8742</v>
       </c>
       <c r="V6" t="n">
-        <v>0.1257</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>0.3144</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.1888</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.5208</v>
+        <v>-0.0504</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.9098</v>
+        <v>-1.3654</v>
       </c>
       <c r="F7" t="n">
-        <v>1.3889</v>
+        <v>1.3151</v>
       </c>
       <c r="G7" t="n">
         <v>-0.1682</v>
@@ -1000,13 +1000,13 @@
         <v>0.3706</v>
       </c>
       <c r="S7" t="n">
-        <v>0.2032</v>
+        <v>0.6737</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.4377</v>
+        <v>0.1066</v>
       </c>
       <c r="U7" t="n">
-        <v>0.6409</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.5769</v>
+        <v>-0.1113</v>
       </c>
       <c r="E8" t="n">
-        <v>-3.1946</v>
+        <v>-2.8028</v>
       </c>
       <c r="F8" t="n">
-        <v>2.6177</v>
+        <v>2.6915</v>
       </c>
       <c r="G8" t="n">
         <v>0.1861</v>
@@ -1078,13 +1078,13 @@
         <v>1.4823</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0405</v>
+        <v>0.5061</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.149</v>
+        <v>-0.7573</v>
       </c>
       <c r="U8" t="n">
-        <v>1.1895</v>
+        <v>1.2634</v>
       </c>
       <c r="V8" t="n">
         <v>3.2728</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>F. QUINTERO DE ARMAS</t>
+          <t>R. RUBIO SANCHEZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.2359</v>
+        <v>-1.2006</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.0315</v>
+        <v>-0.7243000000000001</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.2044</v>
+        <v>-0.4763</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.7911</v>
+        <v>-0.3735</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1306</v>
+        <v>0.4329</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.9216</v>
+        <v>-0.8064</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.2108</v>
+        <v>0.3778</v>
       </c>
       <c r="K9" t="n">
-        <v>0.4207</v>
+        <v>1.0306</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.6315</v>
+        <v>-0.6529</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.5803</v>
+        <v>-0.7513</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.2901</v>
+        <v>-0.5977</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.2901</v>
+        <v>-0.1536</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>-0.1853</v>
       </c>
       <c r="Q9" t="n">
         <v>-0.9264</v>
       </c>
       <c r="R9" t="n">
-        <v>0.9264</v>
+        <v>0.7411</v>
       </c>
       <c r="S9" t="n">
-        <v>0.5551</v>
+        <v>-0.3274</v>
       </c>
       <c r="T9" t="n">
-        <v>0.1057</v>
+        <v>-0.1756</v>
       </c>
       <c r="U9" t="n">
-        <v>0.4494</v>
+        <v>-0.1517</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>-0.3144</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-0.3144</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>R. RUBIO SANCHEZ</t>
+          <t>F. QUINTERO DE ARMAS</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.2985</v>
+        <v>-1.3826</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.8222</v>
+        <v>-1.2274</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.4763</v>
+        <v>-0.1552</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.3735</v>
+        <v>-1.7911</v>
       </c>
       <c r="H10" t="n">
-        <v>0.4329</v>
+        <v>0.1306</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.8064</v>
+        <v>-1.9216</v>
       </c>
       <c r="J10" t="n">
-        <v>0.3778</v>
+        <v>-0.2108</v>
       </c>
       <c r="K10" t="n">
-        <v>1.0306</v>
+        <v>0.4207</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.6529</v>
+        <v>-0.6315</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.7513</v>
+        <v>-1.5803</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.5977</v>
+        <v>-0.2901</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.1536</v>
+        <v>-1.2901</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.1853</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
         <v>-0.9264</v>
       </c>
       <c r="R10" t="n">
-        <v>0.7411</v>
+        <v>0.9264</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.4253</v>
+        <v>0.4085</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.2736</v>
+        <v>-0.0901</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1517</v>
+        <v>0.4986</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.3144</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.3144</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.903</v>
+        <v>-1.781</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.1572</v>
+        <v>-0.9613</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.7458</v>
+        <v>-0.8197</v>
       </c>
       <c r="G11" t="n">
         <v>-1.8343</v>
@@ -1312,13 +1312,13 @@
         <v>0.7411</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.1798</v>
+        <v>-0.0578</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.2736</v>
+        <v>-0.07770000000000001</v>
       </c>
       <c r="U11" t="n">
-        <v>0.09379999999999999</v>
+        <v>0.0199</v>
       </c>
       <c r="V11" t="n">
         <v>-0.63</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.3062</v>
+        <v>-1.8641</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.2583</v>
+        <v>-3.0625</v>
       </c>
       <c r="F12" t="n">
-        <v>0.9522</v>
+        <v>1.1984</v>
       </c>
       <c r="G12" t="n">
         <v>-1.8473</v>
@@ -1390,13 +1390,13 @@
         <v>0.7411</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.2736</v>
+        <v>0.1685</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.4377</v>
+        <v>-0.2419</v>
       </c>
       <c r="U12" t="n">
-        <v>0.1641</v>
+        <v>0.4104</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1423,22 +1423,22 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.659200000000002</v>
+        <v>3.5808</v>
       </c>
       <c r="E13" t="n">
-        <v>-15.0666</v>
+        <v>-14.9888</v>
       </c>
       <c r="F13" t="n">
-        <v>18.7258</v>
+        <v>18.5696</v>
       </c>
       <c r="G13" t="n">
         <v>4.197700000000001</v>
       </c>
       <c r="H13" t="n">
-        <v>3.339999999999999</v>
+        <v>3.34</v>
       </c>
       <c r="I13" t="n">
-        <v>0.8576999999999997</v>
+        <v>0.857700000000001</v>
       </c>
       <c r="J13" t="n">
         <v>2.9139</v>
@@ -1447,10 +1447,10 @@
         <v>3.801</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.8872999999999993</v>
+        <v>-0.8872999999999995</v>
       </c>
       <c r="M13" t="n">
-        <v>1.2839</v>
+        <v>1.283899999999999</v>
       </c>
       <c r="N13" t="n">
         <v>-0.4610000000000001</v>
@@ -1468,16 +1468,16 @@
         <v>10.9317</v>
       </c>
       <c r="S13" t="n">
-        <v>7.148300000000001</v>
+        <v>7.069999999999999</v>
       </c>
       <c r="T13" t="n">
-        <v>-2.0032</v>
+        <v>-1.9253</v>
       </c>
       <c r="U13" t="n">
-        <v>9.151499999999999</v>
+        <v>8.9955</v>
       </c>
       <c r="V13" t="n">
-        <v>1.762700000000001</v>
+        <v>1.7627</v>
       </c>
       <c r="W13" t="n">
         <v>4.4043</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>J. VAZQUEZ SUAREZ</t>
+          <t>A. VEGUILLA SANCHEZ</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.761</v>
+        <v>2.401</v>
       </c>
       <c r="E14" t="n">
-        <v>1.716</v>
+        <v>0.5956</v>
       </c>
       <c r="F14" t="n">
-        <v>1.045</v>
+        <v>1.8054</v>
       </c>
       <c r="G14" t="n">
-        <v>1.0103</v>
+        <v>1.9151</v>
       </c>
       <c r="H14" t="n">
-        <v>1.5634</v>
+        <v>2.6172</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.5531</v>
+        <v>-0.7020999999999999</v>
       </c>
       <c r="J14" t="n">
-        <v>1.8977</v>
+        <v>1.4825</v>
       </c>
       <c r="K14" t="n">
-        <v>2.4048</v>
+        <v>2.6839</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.5071</v>
+        <v>-1.2014</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.8874</v>
+        <v>0.4326</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.8414</v>
+        <v>-0.0667</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.046</v>
+        <v>0.4993</v>
       </c>
       <c r="P14" t="n">
-        <v>1.1117</v>
+        <v>2.0382</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.9264</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
         <v>2.0382</v>
       </c>
       <c r="S14" t="n">
-        <v>0.3246</v>
+        <v>-0.6084000000000001</v>
       </c>
       <c r="T14" t="n">
-        <v>0.4303</v>
+        <v>-0.8869</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.1057</v>
+        <v>0.2785</v>
       </c>
       <c r="V14" t="n">
-        <v>0.3144</v>
+        <v>-0.9439</v>
       </c>
       <c r="W14" t="n">
-        <v>0.3144</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>-0.9439</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>R. HENRIQUE RIBEIRO FORMOSO</t>
+          <t>J. VAZQUEZ SUAREZ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,64 +1579,64 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.6108</v>
+        <v>1.9776</v>
       </c>
       <c r="E15" t="n">
-        <v>-2.3718</v>
+        <v>0.9326</v>
       </c>
       <c r="F15" t="n">
-        <v>4.9827</v>
+        <v>1.045</v>
       </c>
       <c r="G15" t="n">
-        <v>-1.1272</v>
+        <v>1.0103</v>
       </c>
       <c r="H15" t="n">
-        <v>-1.7694</v>
+        <v>1.5634</v>
       </c>
       <c r="I15" t="n">
-        <v>0.6422</v>
+        <v>-0.5531</v>
       </c>
       <c r="J15" t="n">
-        <v>-1.6471</v>
+        <v>1.8977</v>
       </c>
       <c r="K15" t="n">
-        <v>-1.813</v>
+        <v>2.4048</v>
       </c>
       <c r="L15" t="n">
-        <v>0.1659</v>
+        <v>-0.5071</v>
       </c>
       <c r="M15" t="n">
-        <v>0.5199</v>
+        <v>-0.8874</v>
       </c>
       <c r="N15" t="n">
-        <v>0.0436</v>
+        <v>-0.8414</v>
       </c>
       <c r="O15" t="n">
-        <v>0.4763</v>
+        <v>-0.046</v>
       </c>
       <c r="P15" t="n">
-        <v>2.4087</v>
+        <v>1.1117</v>
       </c>
       <c r="Q15" t="n">
         <v>-0.9264</v>
       </c>
       <c r="R15" t="n">
-        <v>3.3352</v>
+        <v>2.0382</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.244</v>
+        <v>-0.4589</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.3716</v>
+        <v>-0.3531</v>
       </c>
       <c r="U15" t="n">
-        <v>1.1276</v>
+        <v>-0.1057</v>
       </c>
       <c r="V15" t="n">
-        <v>1.5733</v>
+        <v>0.3144</v>
       </c>
       <c r="W15" t="n">
-        <v>1.5733</v>
+        <v>0.3144</v>
       </c>
       <c r="X15" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. VEGUILLA SANCHEZ</t>
+          <t>R. HENRIQUE RIBEIRO FORMOSO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.9337</v>
+        <v>1.8</v>
       </c>
       <c r="E16" t="n">
-        <v>0.4976</v>
+        <v>-2.6656</v>
       </c>
       <c r="F16" t="n">
-        <v>1.4361</v>
+        <v>4.4656</v>
       </c>
       <c r="G16" t="n">
-        <v>1.9151</v>
+        <v>-1.1272</v>
       </c>
       <c r="H16" t="n">
-        <v>2.6172</v>
+        <v>-1.7694</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.7020999999999999</v>
+        <v>0.6422</v>
       </c>
       <c r="J16" t="n">
-        <v>1.4825</v>
+        <v>-1.6471</v>
       </c>
       <c r="K16" t="n">
-        <v>2.6839</v>
+        <v>-1.813</v>
       </c>
       <c r="L16" t="n">
-        <v>-1.2014</v>
+        <v>0.1659</v>
       </c>
       <c r="M16" t="n">
-        <v>0.4326</v>
+        <v>0.5199</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.0667</v>
+        <v>0.0436</v>
       </c>
       <c r="O16" t="n">
-        <v>0.4993</v>
+        <v>0.4763</v>
       </c>
       <c r="P16" t="n">
-        <v>2.0382</v>
+        <v>2.4087</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-0.9264</v>
       </c>
       <c r="R16" t="n">
-        <v>2.0382</v>
+        <v>3.3352</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.0757</v>
+        <v>-1.0548</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.9849</v>
+        <v>-1.6654</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.09080000000000001</v>
+        <v>0.6105</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.9439</v>
+        <v>1.5733</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.5733</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.9439</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.8784</v>
+        <v>1.0989</v>
       </c>
       <c r="E17" t="n">
-        <v>1.8298</v>
+        <v>2.0257</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.9514</v>
+        <v>-0.9268</v>
       </c>
       <c r="G17" t="n">
         <v>0.0786</v>
@@ -1780,13 +1780,13 @@
         <v>1.297</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.4972</v>
+        <v>-0.2767</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.6566</v>
+        <v>-0.4607</v>
       </c>
       <c r="U17" t="n">
-        <v>0.1594</v>
+        <v>0.184</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.7354000000000001</v>
+        <v>0.6845</v>
       </c>
       <c r="E18" t="n">
-        <v>-5.3374</v>
+        <v>-5.0436</v>
       </c>
       <c r="F18" t="n">
-        <v>6.0728</v>
+        <v>5.7281</v>
       </c>
       <c r="G18" t="n">
         <v>-0.502</v>
@@ -1858,13 +1858,13 @@
         <v>2.9646</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.8367</v>
+        <v>-0.8875999999999999</v>
       </c>
       <c r="T18" t="n">
-        <v>-1.8056</v>
+        <v>-1.5118</v>
       </c>
       <c r="U18" t="n">
-        <v>0.9689</v>
+        <v>0.6242</v>
       </c>
       <c r="V18" t="n">
         <v>1.8888</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.3549</v>
+        <v>0.4774</v>
       </c>
       <c r="E20" t="n">
-        <v>0.1275</v>
+        <v>0.2254</v>
       </c>
       <c r="F20" t="n">
-        <v>0.2274</v>
+        <v>0.2521</v>
       </c>
       <c r="G20" t="n">
         <v>0.0015</v>
@@ -2014,13 +2014,13 @@
         <v>0.9264</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.573</v>
+        <v>-0.4505</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.6019</v>
+        <v>-0.5039</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0288</v>
+        <v>0.0535</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.1645</v>
+        <v>-0.08</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.1745</v>
+        <v>-0.4683</v>
       </c>
       <c r="F21" t="n">
-        <v>0.339</v>
+        <v>0.3883</v>
       </c>
       <c r="G21" t="n">
         <v>-1.1951</v>
@@ -2092,13 +2092,13 @@
         <v>1.6676</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.3079</v>
+        <v>-0.5524</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.4961</v>
+        <v>-0.7899</v>
       </c>
       <c r="U21" t="n">
-        <v>0.1883</v>
+        <v>0.2375</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>F. BENITEZ SIERRA</t>
+          <t>A. LLAMAS JIMENEZ</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.4412</v>
+        <v>-1.9783</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.8801</v>
+        <v>-5.175</v>
       </c>
       <c r="F22" t="n">
-        <v>1.4389</v>
+        <v>3.1967</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.3591</v>
+        <v>-0.5852000000000001</v>
       </c>
       <c r="H22" t="n">
-        <v>-2.1164</v>
+        <v>-1.8663</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.2427</v>
+        <v>1.2811</v>
       </c>
       <c r="J22" t="n">
-        <v>-2.4841</v>
+        <v>-1.7869</v>
       </c>
       <c r="K22" t="n">
-        <v>-1.8727</v>
+        <v>-2.4611</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.6114000000000001</v>
+        <v>0.6742</v>
       </c>
       <c r="M22" t="n">
-        <v>0.125</v>
+        <v>1.2018</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.2437</v>
+        <v>0.5949</v>
       </c>
       <c r="O22" t="n">
-        <v>0.3687</v>
+        <v>0.6069</v>
       </c>
       <c r="P22" t="n">
-        <v>0.7411</v>
+        <v>-0.1853</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>-2.7793</v>
       </c>
       <c r="R22" t="n">
-        <v>0.7411</v>
+        <v>2.594</v>
       </c>
       <c r="S22" t="n">
-        <v>0.1211</v>
+        <v>-1.2084</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.766</v>
+        <v>-1.2382</v>
       </c>
       <c r="U22" t="n">
-        <v>0.8871</v>
+        <v>0.0298</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.9444</v>
+        <v>0.0005</v>
       </c>
       <c r="W22" t="n">
-        <v>-0.63</v>
+        <v>0.6294</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.3144</v>
+        <v>-0.6289</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A. LLAMAS JIMENEZ</t>
+          <t>F. BENITEZ SIERRA</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.6414</v>
+        <v>-2.4423</v>
       </c>
       <c r="E23" t="n">
-        <v>-5.4688</v>
+        <v>-3.6842</v>
       </c>
       <c r="F23" t="n">
-        <v>2.8274</v>
+        <v>1.2419</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.5852000000000001</v>
+        <v>-2.3591</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.8663</v>
+        <v>-2.1164</v>
       </c>
       <c r="I23" t="n">
-        <v>1.2811</v>
+        <v>-0.2427</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.7869</v>
+        <v>-2.4841</v>
       </c>
       <c r="K23" t="n">
-        <v>-2.4611</v>
+        <v>-1.8727</v>
       </c>
       <c r="L23" t="n">
-        <v>0.6742</v>
+        <v>-0.6114000000000001</v>
       </c>
       <c r="M23" t="n">
-        <v>1.2018</v>
+        <v>0.125</v>
       </c>
       <c r="N23" t="n">
-        <v>0.5949</v>
+        <v>-0.2437</v>
       </c>
       <c r="O23" t="n">
-        <v>0.6069</v>
+        <v>0.3687</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.1853</v>
+        <v>0.7411</v>
       </c>
       <c r="Q23" t="n">
-        <v>-2.7793</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>2.594</v>
+        <v>0.7411</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.8715</v>
+        <v>0.12</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.532</v>
+        <v>-0.5701000000000001</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.3395</v>
+        <v>0.6901</v>
       </c>
       <c r="V23" t="n">
-        <v>0.0005</v>
+        <v>-0.9444</v>
       </c>
       <c r="W23" t="n">
-        <v>0.6294</v>
+        <v>-0.63</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.6289</v>
+        <v>-0.3144</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-7.5936</v>
+        <v>-7.1761</v>
       </c>
       <c r="E24" t="n">
-        <v>-5.4861</v>
+        <v>-5.2903</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.1075</v>
+        <v>-1.8859</v>
       </c>
       <c r="G24" t="n">
         <v>-1.3439</v>
@@ -2326,13 +2326,13 @@
         <v>2.7793</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.8606</v>
+        <v>-1.4431</v>
       </c>
       <c r="T24" t="n">
-        <v>-1.3679</v>
+        <v>-1.172</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.4927</v>
+        <v>-0.2711</v>
       </c>
       <c r="V24" t="n">
         <v>-3.4627</v>
@@ -2359,10 +2359,10 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-2.6154</v>
+        <v>-2.6152</v>
       </c>
       <c r="E25" t="n">
-        <v>-17.9257</v>
+        <v>-17.9256</v>
       </c>
       <c r="F25" t="n">
         <v>15.3104</v>
@@ -2374,10 +2374,10 @@
         <v>-3.177</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.3079000000000002</v>
+        <v>-0.3079</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.4866999999999997</v>
+        <v>-0.4866999999999999</v>
       </c>
       <c r="K25" t="n">
         <v>0.6669999999999996</v>
@@ -2395,7 +2395,7 @@
         <v>0.8459000000000001</v>
       </c>
       <c r="P25" t="n">
-        <v>9.264299999999999</v>
+        <v>9.2643</v>
       </c>
       <c r="Q25" t="n">
         <v>-11.1171</v>
@@ -2404,16 +2404,16 @@
         <v>20.3816</v>
       </c>
       <c r="S25" t="n">
-        <v>-6.8209</v>
+        <v>-6.820799999999999</v>
       </c>
       <c r="T25" t="n">
-        <v>-9.1523</v>
+        <v>-9.152000000000001</v>
       </c>
       <c r="U25" t="n">
-        <v>2.331399999999999</v>
+        <v>2.3313</v>
       </c>
       <c r="V25" t="n">
-        <v>-1.574</v>
+        <v>-1.573999999999999</v>
       </c>
       <c r="W25" t="n">
         <v>2.8305</v>
